--- a/site/exports/uestc-public-administration.xlsx
+++ b/site/exports/uestc-public-administration.xlsx
@@ -453,7 +453,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；官方个人页及研招简介所见部分职业资料，学历时间与师承未披露。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：社会政策导论；讲授；教学／课程开设时间：时间未披露；来源ID：uestc-fanxin-admissions-profile；https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20551?yxsh=16 | 教育管理学；讲授；教学／课程开设时间：时间未披露；来源ID：uestc-fanxin-admissions-profile；https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20551?yxsh=16 | 教育政策；讲授；教学／课程开设时间：时间未披露；来源ID：uestc-fanxin-admissions-profile；https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20551?yxsh=16 | 社会学原理；讲授；教学／课程开设时间：时间未披露；来源ID：uestc-fanxin-admissions-profile；https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20551?yxsh=16</t>
+          <t>分批核实资料，不是完整名录；官方个人页及研招简介所见部分职业资料，学历时间与师承未披露。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：社会政策导论；讲授；教学／课程开设时间：时间未披露；来源ID：uestc-fanxin-admissions-profile；https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20551?yxsh=16 | 教育管理学；讲授；教学／课程开设时间：时间未披露；来源ID：uestc-fanxin-admissions-profile；https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20551?yxsh=16 | 教育政策；讲授；教学／课程开设时间：时间未披露；来源ID：uestc-fanxin-admissions-profile；https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20551?yxsh=16 | 社会学原理；讲授；教学／课程开设时间：时间未披露；来源ID：uestc-fanxin-admissions-profile；https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20551?yxsh=16；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>

--- a/site/exports/uestc-public-administration.xlsx
+++ b/site/exports/uestc-public-administration.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,14 +443,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18.2" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="26.6" customWidth="1" min="8" max="8"/>
@@ -569,10 +569,118 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>康健</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>公共管理学院</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.uestc.edu.cn/kangjian/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期未单独记录）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>当前任职及退休状态未独立核实；导航和当前教师计数保持关闭。；本人导师未见明确具名关系，教授/博导称谓不构成本人的师承。；学习或毕业时间不自动认定为授位日期；法律授位主体、院校地域和985分类未知。；目录解析、原始href与真实浏览器点击分别保留，不互相升格。；作品仅官网书目；未核出版社元数据或全文。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；部分公开职业资料；非完整履历或当前在岗证明；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：公共管理学；未披露；教学／课程开设时间：时间未披露；来源列示本科生课程；不认证本期开课或教学责任。；来源ID：uestc-kangjian-mpa-profile；https://mpa.uestc.edu.cn/info/1033/1495.htm | 行政管理综合实验实践II；未披露；教学／课程开设时间：时间未披露；来源列示本科生课程；不认证本期开课或教学责任。；来源ID：uestc-kangjian-mpa-profile；https://mpa.uestc.edu.cn/info/1033/1495.htm | 城市管理研究前沿；未披露；教学／课程开设时间：时间未披露；来源列示本科生课程；不认证本期开课或教学责任。；来源ID：uestc-kangjian-mpa-profile；https://mpa.uestc.edu.cn/info/1033/1495.htm | 地方政府治理专题研究；未披露；教学／课程开设时间：时间未披露；来源列示硕士生课程；不认证本期开课或教学责任。；来源ID：uestc-kangjian-mpa-profile；https://mpa.uestc.edu.cn/info/1033/1495.htm | MPA学术规范与论文写作；未披露；教学／课程开设时间：时间未披露；来源列示硕士生课程；不认证本期开课或教学责任。；来源ID：uestc-kangjian-mpa-profile；https://mpa.uestc.edu.cn/info/1033/1495.htm；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>梁健</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>公共管理学院</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.uestc.edu.cn/liangjian/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>当前任职及退休状态未独立核实；导航和当前教师计数保持关闭。；本人导师未见明确具名关系，教授/博导称谓不构成本人的师承。；学习或毕业时间不自动认定为授位日期；法律授位主体、院校地域和985分类未知。；目录解析、原始href与真实浏览器点击分别保留，不互相升格。；作品仅官网书目；未核出版社元数据或全文。；本科及硕士经历未披露；2023仅毕业年份，2023-07-14仅入职日，不作为副教授晋升日期。；已读官网论文列表共0条，仅表示该页无具名书目，不断言本人无成果。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,11 +692,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26.6" customWidth="1" min="2" max="2"/>
+    <col width="32.2" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16.8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -979,14 +1087,478 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>康健</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2011-09</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2015-06</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>行政管理</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>来源明确授位，学习/毕业时间不自动提升为授位年月日。 获授由个人简介明确句支持；时间范围来自研招学术经历。毕业/学习止期不转作授位日期或授位年份。</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20595?yxsh=16</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>康健</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2015-09</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>公共管理学</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>来源明确授位，学习/毕业时间不自动提升为授位年月日。 获授由个人简介明确句支持；时间范围来自研招学术经历。毕业/学习止期不转作授位日期或授位年份。</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20595?yxsh=16</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>康健</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>公共管理学</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>来源明确授位，学习/毕业时间不自动提升为授位年月日。 获授由个人简介明确句支持；时间范围来自研招学术经历。毕业/学习止期不转作授位日期或授位年份。</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20595?yxsh=16</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>康健</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>joint_doctoral_training</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>博士生联合培养</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>哈佛大学</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>公共管理学</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>非学位研究或培训经历，不作为学位获授。 联合培养事件不表示哈佛学位获授；不否定另列四川大学博士学位。未从博士后基金项目推定博士后经历。</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20595?yxsh=16</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>康健</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>讲师、副教授</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>来源历史任职记录；机构加入时间不代表职称晋升日，“至今”不证明当前持续任职。 不拆分未明确的职称晋升日期；入职日与经历月份并列保存。</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20595?yxsh=16</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>梁健</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>武汉大学</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>行政管理</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>来源明确授位，学习/毕业时间不自动提升为授位年月日。来源毕业年份：2023年，不作授位年份。</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.uestc.edu.cn/liangjian/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>梁健</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>来源历史任职记录；机构加入时间不代表职称晋升日，“至今”不证明当前持续任职。 来源入职时间字段为2023-07-14，仅表示机构入职，不作为副教授职称晋升日期；任职规范起始日期仍未知。</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.uestc.edu.cn/liangjian/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S5"/>
+  <autoFilter ref="A1:S12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1089,15 +1661,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26.6" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="36.4" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
@@ -1224,12 +1796,120 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>康健</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>基本公共服务均衡性推动共同富裕：效应检验与机制探索</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20595?yxsh=16</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>期刊论文（官网书目）；journal_article</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20595?yxsh=16</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>仅官网书目；未核出版社元数据或全文。；official_publication_list_only</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>作者串、原始标点和书目信息按来源保留，不推作者角色。</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>康健</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>界面营造与信任重塑：人工智能社会治理实验何以实现社区合作治理？——基于成都市七道堰社区试点的案例分析</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20595?yxsh=16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>期刊论文（官网书目）；journal_article</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20595?yxsh=16</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>仅官网书目；未核出版社元数据或全文。；official_publication_list_only</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>作者串、原始标点和书目信息按来源保留，不推作者角色。</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L2"/>
+  <autoFilter ref="A1:L4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1241,7 +1921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1438,13 +2118,263 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>康健</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>uestc-kangjian-profile</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.uestc.edu.cn/kangjian/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>已复核既有必要职业摘录；非本次重抓或现职认证；retained_professional_excerpts_checked</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>康健</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>uestc-kangjian-graduate-profile</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/20595?yxsh=16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>已复核既有必要职业摘录；非本次重抓或现职认证；retained_professional_excerpts_checked</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>康健</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>uestc-kangjian-mpa-profile</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>https://mpa.uestc.edu.cn/info/1033/1495.htm</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>已复核既有必要职业摘录；非本次重抓或现职认证；retained_professional_excerpts_checked</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>康健</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>uestc-mpa-associate-directory</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>https://mpa.uestc.edu.cn/dsjs/fjs.htm</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>已复核既有必要职业摘录；非本次重抓或现职认证；retained_professional_excerpts_checked</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>梁健</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>uestc-liangjian-profile</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.uestc.edu.cn/liangjian/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>已复核既有必要职业摘录；非本次重抓或现职认证；retained_professional_excerpts_checked</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>梁健</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>uestc-public-management-directory</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.uestc.edu.cn/xylb.jsp?id=2023&amp;lang=zh_CN&amp;urltype=tsites.CollegeTeacherList&amp;wbtreeid=1035</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>已复核既有必要职业摘录；非本次重抓或现职认证；retained_professional_excerpts_checked</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>梁健</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>uestc-liangjian-publications</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.uestc.edu.cn/liangjian/zh_CN/lwcg/496507/list/index.htm</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>已复核既有必要职业摘录；非本次重抓或现职认证；retained_professional_excerpts_checked</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/uestc-public-administration.xlsx
+++ b/site/exports/uestc-public-administration.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="18.2" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -675,12 +675,66 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>詹恂</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>公共管理学院</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://mpa.uestc.edu.cn/info/1032/1099.htm</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1994年毕业的学历层次未披露，不能默认本科或学士。；博士学习专业文艺学与页面法学博士标签均原样保留，不补授位。；访学导师英文拼写严格沿用教学个人页，不由中文简介或外部常见拼写纠正、合并实体。；两篇官网书目均未列作者，authors_source_reported为未知，不因个人页署名补入詹恂。；公共管理学院已有范昕；此次是新闻传播专业目的性样本，并非全新学院覆盖。；来源记载职业信息：来源职称表述：教授、硕士生导师。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。；来源记载职业信息：内设单位：新闻传播系。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:K5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -692,11 +746,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="32.2" customWidth="1" min="2" max="2"/>
+    <col width="39.2" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16.8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -774,7 +828,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1544,8 +1598,339 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>詹恂</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>graduation_stage_unspecified</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>毕业</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>四川外语学院</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1994-07</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>外事管理</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>毕业明确，但没有本科/学士阶段和授位表述；保留当时院校名称，不自动改名或补学位。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/10594?yxsh=16</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>詹恂</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1997-09</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2000-06</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2000-06</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>明确于2000年6月取得硕士学位；研究题目不是专业名。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/10594?yxsh=16</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>詹恂</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>文艺学</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>博士毕业和页面法学博士学位标签不升级为明确授位，毕业月不作授位月；不自行推断学位门类与专业如何对应。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源unit：文学与新闻学院</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/10594?yxsh=16</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>詹恂</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>visiting_scholar</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>访问学者</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>美国加州大学圣地亚哥分校</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>访问学者经历不是该校学位；年份为访问阶段范围，不是导师任期。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://i.study.uestc.edu.cn/JOURNALISM/menu/course-principal</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>詹恂</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>visiting_scholar</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>访问学者</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>美国威廉玛丽学院</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>来源仅标2019；start/end以同一年表示该年的访问阶段，月份和具体区间未知。访问不作学位。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；本轮规范仅保留来源所记2019年访问事件；起止时间未知，不把单一年份扩为起止区间，不作学位事件。</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://i.study.uestc.edu.cn/JOURNALISM/menu/course-principal</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S12"/>
+  <autoFilter ref="A1:S17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1559,6 +1944,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1570,18 +1960,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="32.2" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22.4" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1649,8 +2039,112 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>詹恂</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>DAN HALLIN</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>stage_specific_mentorship</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>加州大学圣地亚哥分校访问学者阶段</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；Source-mentioned name only; no independent mentor identity node, biography or present employment. Stage dates are in education event; exact supervision start/end unknown. Not a formal dissertation-advisor assertion.；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>https://i.study.uestc.edu.cn/JOURNALISM/menu/course-principal</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>詹恂</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>JENIFFER BICKHAM MENDAZ</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>stage_specific_mentorship</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>威廉玛丽学院访问学者阶段</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；Source-mentioned name only; no independent mentor identity node, biography or present employment. Stage dates are in education event; exact supervision start/end unknown. Not a formal dissertation-advisor assertion.；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://i.study.uestc.edu.cn/JOURNALISM/menu/course-principal</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L3"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1661,7 +2155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1673,7 +2167,7 @@
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
-    <col width="49" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1900,8 +2394,104 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>詹恂</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>微信用户持续使用意向影响因素及使用与满足研究</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://mpa.uestc.edu.cn/info/1032/1099.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://mpa.uestc.edu.cn/info/1032/1099.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源书目信息（publication_date_label）：2014.11；来源书目信息（authors_status）：not_disclosed_in_selected_entry; null means unknown, not anonymous authorship</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>詹恂</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>微信使用对人际传播的影响研究</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://mpa.uestc.edu.cn/info/1032/1099.htm</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://mpa.uestc.edu.cn/info/1032/1099.htm</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源书目信息（publication_date_label）：2013.12；来源书目信息（authors_status）：not_disclosed_in_selected_entry; null means unknown, not anonymous authorship</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1910,6 +2500,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1921,14 +2515,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="50.4" customWidth="1" min="2" max="2"/>
+    <col width="61.59999999999999" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2361,8 +2955,156 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>詹恂</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-uestc-zhanxun-s001-d0dde51c2125</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>https://mpa.uestc.edu.cn/info/1032/1099.htm</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:38:42Z</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>詹恂</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-uestc-zhanxun-s002-1b7fcae7bb97</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>https://yjsjy.uestc.edu.cn/gmis/jcsjgl/dsfc/dsgrjj/10594?yxsh=16</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:39:43Z</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>詹恂</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-uestc-zhanxun-s003-bb75cc4a8d20</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>https://i.study.uestc.edu.cn/JOURNALISM/menu/course-principal</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:39:18Z</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>詹恂</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-uestc-zhanxun-s004-cdd7f73df09c</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>https://mpa.uestc.edu.cn/dsjs/js_yjy_.htm</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:39:01Z</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -2375,6 +3117,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/uestc-public-administration.xlsx
+++ b/site/exports/uestc-public-administration.xlsx
@@ -1700,7 +1700,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L14" s="2" t="b">
@@ -1775,7 +1775,7 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
